--- a/artfynd/A 57157-2021 artfynd.xlsx
+++ b/artfynd/A 57157-2021 artfynd.xlsx
@@ -1182,12 +1182,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Josefin Stagnell</t>
+          <t>Josefin Hagernäs</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Josefin Stagnell, Leif Persson</t>
+          <t>Josefin Hagernäs, Leif Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 57157-2021 artfynd.xlsx
+++ b/artfynd/A 57157-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1192,6 +1192,327 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128279620</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91372</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ålpussen, Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>619714</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6568424</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128279553</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91372</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ålpussen, Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>619720</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6568425</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128279660</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91372</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ålpussen, Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>619695</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6568431</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57157-2021 artfynd.xlsx
+++ b/artfynd/A 57157-2021 artfynd.xlsx
@@ -1197,7 +1197,7 @@
         <v>128279620</v>
       </c>
       <c r="B6" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128279553</v>
       </c>
       <c r="B7" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128279660</v>
       </c>
       <c r="B8" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57157-2021 artfynd.xlsx
+++ b/artfynd/A 57157-2021 artfynd.xlsx
@@ -1197,7 +1197,7 @@
         <v>128279620</v>
       </c>
       <c r="B6" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128279553</v>
       </c>
       <c r="B7" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128279660</v>
       </c>
       <c r="B8" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57157-2021 artfynd.xlsx
+++ b/artfynd/A 57157-2021 artfynd.xlsx
@@ -1197,7 +1197,7 @@
         <v>128279620</v>
       </c>
       <c r="B6" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128279553</v>
       </c>
       <c r="B7" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128279660</v>
       </c>
       <c r="B8" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57157-2021 artfynd.xlsx
+++ b/artfynd/A 57157-2021 artfynd.xlsx
@@ -1197,7 +1197,7 @@
         <v>128279620</v>
       </c>
       <c r="B6" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128279553</v>
       </c>
       <c r="B7" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128279660</v>
       </c>
       <c r="B8" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57157-2021 artfynd.xlsx
+++ b/artfynd/A 57157-2021 artfynd.xlsx
@@ -1197,7 +1197,7 @@
         <v>128279620</v>
       </c>
       <c r="B6" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128279553</v>
       </c>
       <c r="B7" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128279660</v>
       </c>
       <c r="B8" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57157-2021 artfynd.xlsx
+++ b/artfynd/A 57157-2021 artfynd.xlsx
@@ -1197,7 +1197,7 @@
         <v>128279620</v>
       </c>
       <c r="B6" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128279553</v>
       </c>
       <c r="B7" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128279660</v>
       </c>
       <c r="B8" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57157-2021 artfynd.xlsx
+++ b/artfynd/A 57157-2021 artfynd.xlsx
@@ -1197,7 +1197,7 @@
         <v>128279620</v>
       </c>
       <c r="B6" t="n">
-        <v>91514</v>
+        <v>91524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>128279553</v>
       </c>
       <c r="B7" t="n">
-        <v>91514</v>
+        <v>91524</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128279660</v>
       </c>
       <c r="B8" t="n">
-        <v>91514</v>
+        <v>91524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57157-2021 artfynd.xlsx
+++ b/artfynd/A 57157-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116114659</v>
+        <v>131453309</v>
       </c>
       <c r="B2" t="n">
-        <v>96697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224364</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ulva, Srm</t>
+          <t>Ulva, Ulva, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619861</v>
+        <v>620171</v>
       </c>
       <c r="R2" t="n">
-        <v>6568443</v>
+        <v>6568183</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,74 +764,88 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Åkerholm</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Åkerholm</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116141417</v>
+        <v>128279553</v>
       </c>
       <c r="B3" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ålpussen (Ålpussen), Srm</t>
+          <t>Ålpussen, Ålpussen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619835</v>
+        <v>619720</v>
       </c>
       <c r="R3" t="n">
-        <v>6568448</v>
+        <v>6568425</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +872,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,26 +898,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -919,15 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116128130</v>
+        <v>128279620</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ålpussen (Ålpussen), Srm</t>
+          <t>Ålpussen, Ålpussen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619669</v>
+        <v>619714</v>
       </c>
       <c r="R4" t="n">
-        <v>6568438</v>
+        <v>6568424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,22 +979,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,31 +1005,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1061,15 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118470189</v>
+        <v>128279660</v>
       </c>
       <c r="B5" t="n">
-        <v>56186</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,55 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ulva, Srm</t>
+          <t>Ålpussen, Ålpussen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620174</v>
+        <v>619695</v>
       </c>
       <c r="R5" t="n">
-        <v>6568222</v>
+        <v>6568431</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,22 +1086,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,44 +1116,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Josefin Hagernäs</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Josefin Hagernäs, Leif Persson</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128279620</v>
+        <v>118893171</v>
       </c>
       <c r="B6" t="n">
-        <v>91524</v>
+        <v>91282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>5685</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1229,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619714</v>
+        <v>619818</v>
       </c>
       <c r="R6" t="n">
-        <v>6568424</v>
+        <v>6568478</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,22 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,6 +1219,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1301,45 +1255,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128279553</v>
+        <v>116128130</v>
       </c>
       <c r="B7" t="n">
-        <v>91524</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ålpussen, Ålpussen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619720</v>
+        <v>619669</v>
       </c>
       <c r="R7" t="n">
-        <v>6568425</v>
+        <v>6568438</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,22 +1325,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,6 +1351,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1408,45 +1392,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128279660</v>
+        <v>116588127</v>
       </c>
       <c r="B8" t="n">
-        <v>91524</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ålpussen, Ålpussen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619695</v>
+        <v>619850</v>
       </c>
       <c r="R8" t="n">
-        <v>6568431</v>
+        <v>6568479</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,22 +1462,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,6 +1488,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1512,6 +1521,1956 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>116588136</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ålpussen, Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>619818</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6568478</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119395183</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ulvaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>619810</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6568471</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>116141417</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ålpussen, Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>619835</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6568448</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>116588118</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ålpussen, Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>619834</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6568479</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>21:09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118470189</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ulva, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>620174</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6568222</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>23:02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>23:02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Josefin Hagernäs</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Josefin Hagernäs, Leif Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>116041685</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Talludden, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>620110</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6568354</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växer bland mossiga stenblock och äldre gran o tall.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>116044363</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ulva, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>620144</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6568325</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer under tall bland senvuxna granar.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>116093330</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ulva, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>620165</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6568258</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>116093483</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ulva, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>620178</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6568258</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>116114722</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ulva, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>619918</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6568445</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna Åkerholm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna Åkerholm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>116114762</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ulva, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>620153</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6568229</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anna Åkerholm</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anna Åkerholm</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123064028</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ulva, Ulva, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>620190</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6568243</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132545452</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ulvaskogen, V om Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>619700</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6568402</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132545177</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ulvaskogen, V om Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>619700</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6568402</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132545209</v>
+      </c>
+      <c r="B23" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ulvaskogen, V om Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>619700</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6568402</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132545263</v>
+      </c>
+      <c r="B24" t="n">
+        <v>107397</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>224263</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Praktgulplister</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lamiastrum galeobdolon subsp. argentatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Smejkal) Stace</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ulvaskogen, V om Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>619700</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6568402</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>116114659</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ulva, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>619861</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6568443</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anna Åkerholm</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anna Åkerholm</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57157-2021 artfynd.xlsx
+++ b/artfynd/A 57157-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -804,6 +809,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131453309</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279553</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279620</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279660</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118893171</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1389,6 +1419,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116128130</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1521,6 +1556,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116588127</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1653,6 +1693,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116588136</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1754,6 +1799,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119395183</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1886,6 +1936,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116141417</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2018,6 +2073,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116588118</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2146,6 +2206,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118470189</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2274,6 +2339,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116041685</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2398,6 +2468,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116044363</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2517,6 +2592,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116093330</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2636,6 +2716,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116093483</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2738,6 +2823,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116114722</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2840,6 +2930,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116114762</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2961,6 +3056,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123064028</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3063,6 +3163,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132545452</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3165,6 +3270,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132545177</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3267,6 +3377,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132545209</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3369,6 +3484,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132545263</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3471,8 +3591,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116114659</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>